--- a/src/includes/excel/FORM1.xlsx
+++ b/src/includes/excel/FORM1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ProEva\src\includes\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35CF59B-3AED-4FD6-B903-CC73227C03AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4874F9-53A3-44E9-BFC2-E5D0261E0668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12135" yWindow="0" windowWidth="12135" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24510" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form 1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>Mode of Implementation</t>
   </si>
@@ -190,9 +190,6 @@
   </si>
   <si>
     <t>Date:</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t xml:space="preserve">Implementing Agency: </t>
@@ -540,25 +537,39 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -568,11 +579,25 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -583,45 +608,17 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -865,174 +862,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="X1" s="29" t="s">
+      <c r="X1" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="Y1" s="30"/>
+      <c r="Y1" s="57"/>
     </row>
     <row r="3" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="57"/>
     </row>
     <row r="4" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="57"/>
+      <c r="R4" s="57"/>
+      <c r="S4" s="57"/>
+      <c r="T4" s="57"/>
+      <c r="U4" s="57"/>
+      <c r="V4" s="57"/>
+      <c r="W4" s="57"/>
+      <c r="X4" s="57"/>
+      <c r="Y4" s="57"/>
     </row>
     <row r="5" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="32"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="57"/>
+      <c r="V5" s="57"/>
+      <c r="W5" s="57"/>
+      <c r="X5" s="57"/>
+      <c r="Y5" s="57"/>
     </row>
     <row r="8" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="33" t="s">
+      <c r="F10" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="G10" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="33" t="s">
+      <c r="H10" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="36" t="s">
+      <c r="I10" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="42"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="33" t="s">
+      <c r="J10" s="44"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="M10" s="33" t="s">
+      <c r="M10" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="N10" s="33" t="s">
+      <c r="N10" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="O10" s="36" t="s">
+      <c r="O10" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="33" t="s">
+      <c r="P10" s="45"/>
+      <c r="Q10" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="R10" s="33" t="s">
+      <c r="R10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="S10" s="33" t="s">
+      <c r="S10" s="46" t="s">
         <v>17</v>
       </c>
       <c r="T10" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="U10" s="33" t="s">
+      <c r="U10" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="V10" s="33" t="s">
+      <c r="V10" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="W10" s="33" t="s">
+      <c r="W10" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="X10" s="33" t="s">
+      <c r="X10" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="Y10" s="33" t="s">
+      <c r="Y10" s="46" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:25" ht="30" x14ac:dyDescent="0.25">
-      <c r="B11" s="34"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
       <c r="I11" s="3" t="s">
         <v>24</v>
       </c>
@@ -1042,47 +1039,47 @@
       <c r="K11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="47"/>
+      <c r="N11" s="47"/>
       <c r="O11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="34"/>
-      <c r="W11" s="34"/>
-      <c r="X11" s="34"/>
-      <c r="Y11" s="34"/>
+      <c r="Q11" s="47"/>
+      <c r="R11" s="47"/>
+      <c r="S11" s="47"/>
+      <c r="T11" s="47"/>
+      <c r="U11" s="47"/>
+      <c r="V11" s="47"/>
+      <c r="W11" s="47"/>
+      <c r="X11" s="47"/>
+      <c r="Y11" s="47"/>
     </row>
     <row r="12" spans="2:25" s="10" customFormat="1" ht="198" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="53"/>
-      <c r="P12" s="53"/>
-      <c r="Q12" s="54"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="38"/>
       <c r="R12" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="S12" s="57"/>
-      <c r="T12" s="56"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="29"/>
       <c r="U12" s="26"/>
       <c r="V12" s="26"/>
       <c r="W12" s="24"/>
@@ -1090,385 +1087,337 @@
       <c r="Y12" s="1"/>
     </row>
     <row r="13" spans="2:25" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="52"/>
-      <c r="Q13" s="55"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="39"/>
       <c r="R13" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="S13" s="58"/>
-      <c r="T13" s="59"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="32"/>
       <c r="U13" s="2"/>
-      <c r="V13" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="W13" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
     </row>
     <row r="14" spans="2:25" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="55"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
+      <c r="N14" s="37"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="39"/>
       <c r="R14" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="S14" s="58"/>
-      <c r="T14" s="60"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="33"/>
       <c r="U14" s="2"/>
-      <c r="V14" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="W14" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="V14" s="27"/>
+      <c r="W14" s="27"/>
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
     </row>
     <row r="15" spans="2:25" s="10" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="52"/>
-      <c r="Q15" s="55"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="54"/>
+      <c r="N15" s="37"/>
+      <c r="O15" s="50"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="39"/>
       <c r="R15" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="S15" s="58"/>
-      <c r="T15" s="60"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="33"/>
       <c r="U15" s="2"/>
-      <c r="V15" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="W15" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
     </row>
     <row r="16" spans="2:25" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="55"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="54"/>
+      <c r="N16" s="37"/>
+      <c r="O16" s="50"/>
+      <c r="P16" s="50"/>
+      <c r="Q16" s="39"/>
       <c r="R16" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="S16" s="58"/>
-      <c r="T16" s="60"/>
-      <c r="U16" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="S16" s="31"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="27"/>
       <c r="V16" s="6"/>
-      <c r="W16" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="W16" s="27"/>
       <c r="X16" s="6"/>
       <c r="Y16" s="6"/>
     </row>
     <row r="17" spans="2:25" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="55"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="54"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="50"/>
+      <c r="P17" s="50"/>
+      <c r="Q17" s="39"/>
       <c r="R17" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="S17" s="58"/>
-      <c r="T17" s="60"/>
-      <c r="U17" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="S17" s="31"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="27"/>
       <c r="V17" s="6"/>
-      <c r="W17" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="W17" s="27"/>
       <c r="X17" s="6"/>
       <c r="Y17" s="6"/>
     </row>
     <row r="18" spans="2:25" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="52"/>
-      <c r="Q18" s="55"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="50"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="39"/>
       <c r="R18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="S18" s="58"/>
-      <c r="T18" s="60"/>
-      <c r="U18" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="S18" s="31"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="27"/>
       <c r="V18" s="6"/>
-      <c r="W18" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="W18" s="27"/>
       <c r="X18" s="6"/>
       <c r="Y18" s="6"/>
     </row>
     <row r="19" spans="2:25" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="52"/>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="55"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="54"/>
+      <c r="N19" s="37"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="50"/>
+      <c r="Q19" s="39"/>
       <c r="R19" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="S19" s="58"/>
-      <c r="T19" s="60"/>
-      <c r="U19" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="S19" s="31"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="27"/>
       <c r="V19" s="6"/>
-      <c r="W19" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="W19" s="27"/>
       <c r="X19" s="6"/>
       <c r="Y19" s="6"/>
     </row>
     <row r="20" spans="2:25" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="52"/>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="55"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="54"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="50"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="39"/>
       <c r="R20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="S20" s="58"/>
-      <c r="T20" s="60"/>
-      <c r="U20" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="S20" s="31"/>
+      <c r="T20" s="33"/>
+      <c r="U20" s="27"/>
       <c r="V20" s="6"/>
-      <c r="W20" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="W20" s="27"/>
       <c r="X20" s="6"/>
       <c r="Y20" s="6"/>
     </row>
     <row r="21" spans="2:25" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="55"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="50"/>
+      <c r="Q21" s="39"/>
       <c r="R21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S21" s="58"/>
-      <c r="T21" s="60"/>
-      <c r="U21" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="S21" s="31"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="27"/>
       <c r="V21" s="6"/>
-      <c r="W21" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="W21" s="27"/>
       <c r="X21" s="6"/>
       <c r="Y21" s="6"/>
     </row>
     <row r="22" spans="2:25" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="44"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="46"/>
-      <c r="M22" s="46"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="52"/>
-      <c r="P22" s="52"/>
-      <c r="Q22" s="55"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="50"/>
+      <c r="P22" s="50"/>
+      <c r="Q22" s="39"/>
       <c r="R22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S22" s="58"/>
-      <c r="T22" s="60"/>
-      <c r="U22" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="V22" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="S22" s="31"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="27"/>
+      <c r="V22" s="27"/>
       <c r="W22" s="6"/>
       <c r="X22" s="6"/>
       <c r="Y22" s="6"/>
     </row>
     <row r="23" spans="2:25" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="46"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="52"/>
-      <c r="P23" s="52"/>
-      <c r="Q23" s="55"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="50"/>
+      <c r="P23" s="50"/>
+      <c r="Q23" s="39"/>
       <c r="R23" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="S23" s="58"/>
-      <c r="T23" s="60"/>
-      <c r="U23" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="V23" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="S23" s="31"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
       <c r="W23" s="6"/>
       <c r="X23" s="6"/>
       <c r="Y23" s="6"/>
     </row>
     <row r="24" spans="2:25" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44"/>
-      <c r="K24" s="44"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="52"/>
-      <c r="P24" s="52"/>
-      <c r="Q24" s="55"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="50"/>
+      <c r="P24" s="50"/>
+      <c r="Q24" s="39"/>
       <c r="R24" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="S24" s="58"/>
-      <c r="T24" s="60"/>
-      <c r="U24" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="V24" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="S24" s="31"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="27"/>
       <c r="W24" s="12"/>
       <c r="X24" s="12"/>
       <c r="Y24" s="6"/>
@@ -1607,91 +1556,91 @@
       <c r="B30" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="38"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="39"/>
-      <c r="K30" s="39"/>
-      <c r="L30" s="39"/>
-      <c r="M30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="42"/>
       <c r="N30" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="O30" s="38"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="39"/>
-      <c r="S30" s="39"/>
-      <c r="T30" s="39"/>
-      <c r="U30" s="39"/>
-      <c r="V30" s="39"/>
-      <c r="W30" s="39"/>
-      <c r="X30" s="39"/>
-      <c r="Y30" s="40"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="41"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="42"/>
     </row>
     <row r="31" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="42"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="37"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="44"/>
+      <c r="L31" s="44"/>
+      <c r="M31" s="45"/>
       <c r="N31" s="4"/>
-      <c r="O31" s="41" t="s">
+      <c r="O31" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="42"/>
-      <c r="R31" s="42"/>
-      <c r="S31" s="42"/>
-      <c r="T31" s="42"/>
-      <c r="U31" s="42"/>
-      <c r="V31" s="42"/>
-      <c r="W31" s="42"/>
-      <c r="X31" s="42"/>
-      <c r="Y31" s="37"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="44"/>
+      <c r="S31" s="44"/>
+      <c r="T31" s="44"/>
+      <c r="U31" s="44"/>
+      <c r="V31" s="44"/>
+      <c r="W31" s="44"/>
+      <c r="X31" s="44"/>
+      <c r="Y31" s="45"/>
     </row>
     <row r="32" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="41"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="37"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="45"/>
       <c r="N32" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="O32" s="41"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="42"/>
-      <c r="S32" s="42"/>
-      <c r="T32" s="42"/>
-      <c r="U32" s="42"/>
-      <c r="V32" s="42"/>
-      <c r="W32" s="42"/>
-      <c r="X32" s="42"/>
-      <c r="Y32" s="37"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="44"/>
+      <c r="S32" s="44"/>
+      <c r="T32" s="44"/>
+      <c r="U32" s="44"/>
+      <c r="V32" s="44"/>
+      <c r="W32" s="44"/>
+      <c r="X32" s="44"/>
+      <c r="Y32" s="45"/>
     </row>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2667,25 +2616,19 @@
     <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B12:B24"/>
-    <mergeCell ref="C12:C24"/>
-    <mergeCell ref="D12:D24"/>
-    <mergeCell ref="E12:E24"/>
-    <mergeCell ref="F12:F24"/>
-    <mergeCell ref="Q12:Q24"/>
-    <mergeCell ref="O30:Y30"/>
-    <mergeCell ref="O31:Y31"/>
-    <mergeCell ref="O32:Y32"/>
-    <mergeCell ref="R10:R11"/>
-    <mergeCell ref="S10:S11"/>
-    <mergeCell ref="T10:T11"/>
-    <mergeCell ref="U10:U11"/>
-    <mergeCell ref="V10:V11"/>
-    <mergeCell ref="W10:W11"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="O12:O24"/>
-    <mergeCell ref="P12:P24"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="B3:Y3"/>
+    <mergeCell ref="B4:Y4"/>
+    <mergeCell ref="B5:Y5"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="C30:M30"/>
     <mergeCell ref="C31:M31"/>
     <mergeCell ref="C32:M32"/>
@@ -2701,19 +2644,25 @@
     <mergeCell ref="L12:L24"/>
     <mergeCell ref="M12:M24"/>
     <mergeCell ref="N12:N24"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="B3:Y3"/>
-    <mergeCell ref="B4:Y4"/>
-    <mergeCell ref="B5:Y5"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="Q10:Q11"/>
+    <mergeCell ref="Q12:Q24"/>
+    <mergeCell ref="O30:Y30"/>
+    <mergeCell ref="O31:Y31"/>
+    <mergeCell ref="O32:Y32"/>
+    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="S10:S11"/>
+    <mergeCell ref="T10:T11"/>
+    <mergeCell ref="U10:U11"/>
+    <mergeCell ref="V10:V11"/>
+    <mergeCell ref="W10:W11"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="O12:O24"/>
+    <mergeCell ref="P12:P24"/>
+    <mergeCell ref="B12:B24"/>
+    <mergeCell ref="C12:C24"/>
+    <mergeCell ref="D12:D24"/>
+    <mergeCell ref="E12:E24"/>
+    <mergeCell ref="F12:F24"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D12:D29" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -2975,6 +2924,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3fe2ab7c-8d91-458b-bd16-bbbac8e4a53b" xsi:nil="true"/>
@@ -2983,15 +2941,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3014,6 +2963,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BDA76A7-1A3B-4560-B332-0A3377E9B9A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{238C9514-BABF-4361-80F9-4D3DC6B4D0D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3022,12 +2979,4 @@
     <ds:schemaRef ds:uri="2a4f4df2-35ea-41c7-9e83-0ea62a436e0b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BDA76A7-1A3B-4560-B332-0A3377E9B9A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>